--- a/ParaBank Test Case Design.xlsx
+++ b/ParaBank Test Case Design.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8595DE02-0C4A-4154-86AA-7D2F67344FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tifam\Desktop\Parabank Testing Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10279A9-BF37-4F22-96EB-533D7F592976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abdelrahman" sheetId="9" r:id="rId1"/>
@@ -35,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="869">
   <si>
     <t>TC ID</t>
   </si>
@@ -5049,12 +5054,15 @@
   <si>
     <t>DB persistence check</t>
   </si>
+  <si>
+    <t>Bug_Invalid_Register_01</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6705,25 +6713,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F725057C-2532-4778-8990-23C8BC331D7B}">
   <dimension ref="A1:M96"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="24" customWidth="1"/>
-    <col min="9" max="9" width="19.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="8" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="178" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.28515625" style="183" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="23.6640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="24" customWidth="1"/>
+    <col min="9" max="9" width="19.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="178" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.33203125" style="183" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -6764,7 +6772,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="54" customFormat="1" ht="23.25">
+    <row r="2" spans="1:13" s="54" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="44"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
@@ -6783,7 +6791,7 @@
       <c r="L2" s="179"/>
       <c r="M2" s="46"/>
     </row>
-    <row r="3" spans="1:13" ht="72.75">
+    <row r="3" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
@@ -6824,7 +6832,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="72.75">
+    <row r="4" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
         <v>28</v>
       </c>
@@ -6865,7 +6873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="72.75">
+    <row r="5" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
         <v>37</v>
       </c>
@@ -6903,7 +6911,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="72.75">
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>43</v>
       </c>
@@ -6941,7 +6949,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="72.75">
+    <row r="7" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
         <v>48</v>
       </c>
@@ -6979,7 +6987,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="72.75">
+    <row r="8" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
         <v>53</v>
       </c>
@@ -7017,7 +7025,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="115.5">
+    <row r="9" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
         <v>58</v>
       </c>
@@ -7055,7 +7063,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="72.75">
+    <row r="10" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>64</v>
       </c>
@@ -7090,7 +7098,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="57.75">
+    <row r="11" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
         <v>73</v>
       </c>
@@ -7125,7 +7133,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="57.75">
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
         <v>77</v>
       </c>
@@ -7163,7 +7171,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="72.75">
+    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
         <v>83</v>
       </c>
@@ -7201,7 +7209,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="57.75">
+    <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
         <v>89</v>
       </c>
@@ -7236,7 +7244,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="72.75">
+    <row r="15" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
         <v>96</v>
       </c>
@@ -7271,7 +7279,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="72.75">
+    <row r="16" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
         <v>100</v>
       </c>
@@ -7306,7 +7314,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="72.75">
+    <row r="17" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
         <v>104</v>
       </c>
@@ -7341,7 +7349,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="87">
+    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
         <v>109</v>
       </c>
@@ -7379,7 +7387,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="138" customHeight="1">
+    <row r="19" spans="1:13" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
         <v>118</v>
       </c>
@@ -7420,7 +7428,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="13" customFormat="1" ht="23.25">
+    <row r="20" spans="1:13" s="13" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A20" s="55"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -7437,7 +7445,7 @@
       <c r="L20" s="180"/>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" spans="1:13" s="39" customFormat="1" ht="72.75">
+    <row r="21" spans="1:13" s="39" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="74" t="s">
         <v>128</v>
       </c>
@@ -7474,7 +7482,7 @@
       <c r="L21" s="182"/>
       <c r="M21" s="78"/>
     </row>
-    <row r="22" spans="1:13" s="39" customFormat="1" ht="87">
+    <row r="22" spans="1:13" s="39" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="74" t="s">
         <v>135</v>
       </c>
@@ -7513,7 +7521,7 @@
       </c>
       <c r="M22" s="78"/>
     </row>
-    <row r="23" spans="1:13" s="25" customFormat="1" ht="87">
+    <row r="23" spans="1:13" s="25" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="68" t="s">
         <v>143</v>
       </c>
@@ -7550,7 +7558,7 @@
       <c r="L23" s="182"/>
       <c r="M23" s="71"/>
     </row>
-    <row r="24" spans="1:13" s="59" customFormat="1" ht="87">
+    <row r="24" spans="1:13" s="59" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="81" t="s">
         <v>148</v>
       </c>
@@ -7587,7 +7595,7 @@
       <c r="L24" s="182"/>
       <c r="M24" s="85"/>
     </row>
-    <row r="25" spans="1:13" s="98" customFormat="1" ht="87">
+    <row r="25" spans="1:13" s="98" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="97" t="s">
         <v>153</v>
       </c>
@@ -7624,7 +7632,7 @@
       <c r="L25" s="182"/>
       <c r="M25" s="101"/>
     </row>
-    <row r="26" spans="1:13" s="39" customFormat="1" ht="72.75">
+    <row r="26" spans="1:13" s="39" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="74" t="s">
         <v>158</v>
       </c>
@@ -7661,7 +7669,7 @@
       <c r="L26" s="182"/>
       <c r="M26" s="78"/>
     </row>
-    <row r="27" spans="1:13" s="25" customFormat="1" ht="130.5">
+    <row r="27" spans="1:13" s="25" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A27" s="68" t="s">
         <v>166</v>
       </c>
@@ -7702,7 +7710,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="63" customFormat="1" ht="20.25">
+    <row r="28" spans="1:13" s="63" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A28" s="79"/>
       <c r="B28" s="80" t="s">
         <v>174</v>
@@ -7714,7 +7722,7 @@
       <c r="K28" s="64"/>
       <c r="L28" s="184"/>
     </row>
-    <row r="29" spans="1:13" s="26" customFormat="1" ht="115.5">
+    <row r="29" spans="1:13" s="26" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A29" s="74" t="s">
         <v>175</v>
       </c>
@@ -7751,7 +7759,7 @@
       <c r="L29" s="183"/>
       <c r="M29" s="111"/>
     </row>
-    <row r="30" spans="1:13" s="26" customFormat="1" ht="57.75">
+    <row r="30" spans="1:13" s="26" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="74" t="s">
         <v>180</v>
       </c>
@@ -7788,7 +7796,7 @@
       <c r="L30" s="183"/>
       <c r="M30" s="111"/>
     </row>
-    <row r="31" spans="1:13" s="60" customFormat="1" ht="87">
+    <row r="31" spans="1:13" s="60" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A31" s="68" t="s">
         <v>184</v>
       </c>
@@ -7825,7 +7833,7 @@
       <c r="L31" s="183"/>
       <c r="M31" s="112"/>
     </row>
-    <row r="32" spans="1:13" ht="87">
+    <row r="32" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>189</v>
       </c>
@@ -7860,7 +7868,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="87">
+    <row r="33" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>194</v>
       </c>
@@ -7898,7 +7906,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="87">
+    <row r="34" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>201</v>
       </c>
@@ -7936,7 +7944,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="101.25">
+    <row r="35" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>207</v>
       </c>
@@ -7971,7 +7979,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="63" customFormat="1" ht="36">
+    <row r="36" spans="1:13" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A36" s="65"/>
       <c r="B36" s="43" t="s">
         <v>212</v>
@@ -7983,7 +7991,7 @@
       <c r="K36" s="64"/>
       <c r="L36" s="184"/>
     </row>
-    <row r="37" spans="1:13" ht="115.5">
+    <row r="37" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>213</v>
       </c>
@@ -8021,7 +8029,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="115.5">
+    <row r="38" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>220</v>
       </c>
@@ -8059,7 +8067,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="130.5">
+    <row r="39" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>226</v>
       </c>
@@ -8097,7 +8105,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="130.5">
+    <row r="40" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>232</v>
       </c>
@@ -8135,7 +8143,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="130.5">
+    <row r="41" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>238</v>
       </c>
@@ -8173,7 +8181,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="144.75">
+    <row r="42" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
         <v>243</v>
       </c>
@@ -8211,7 +8219,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="144.75">
+    <row r="43" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A43" s="31" t="s">
         <v>248</v>
       </c>
@@ -8252,7 +8260,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="144.75">
+    <row r="44" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A44" s="20" t="s">
         <v>255</v>
       </c>
@@ -8287,7 +8295,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="144.75">
+    <row r="45" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>261</v>
       </c>
@@ -8322,7 +8330,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="144.75">
+    <row r="46" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>267</v>
       </c>
@@ -8357,7 +8365,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="144.75">
+    <row r="47" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>271</v>
       </c>
@@ -8392,7 +8400,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="130.5">
+    <row r="48" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>275</v>
       </c>
@@ -8427,7 +8435,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="63" customFormat="1" ht="18">
+    <row r="49" spans="1:13" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A49" s="66"/>
       <c r="B49" s="52" t="s">
         <v>279</v>
@@ -8439,7 +8447,7 @@
       <c r="K49" s="174"/>
       <c r="L49" s="184"/>
     </row>
-    <row r="50" spans="1:13" ht="72.75">
+    <row r="50" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>280</v>
       </c>
@@ -8474,7 +8482,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="72.75">
+    <row r="51" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>285</v>
       </c>
@@ -8509,7 +8517,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="87">
+    <row r="52" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>290</v>
       </c>
@@ -8544,7 +8552,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="87">
+    <row r="53" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>293</v>
       </c>
@@ -8579,7 +8587,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="87">
+    <row r="54" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>299</v>
       </c>
@@ -8614,7 +8622,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="87">
+    <row r="55" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="153" t="s">
         <v>305</v>
       </c>
@@ -8649,7 +8657,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="126" customFormat="1" ht="87">
+    <row r="56" spans="1:13" s="126" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A56" s="144" t="s">
         <v>311</v>
       </c>
@@ -8688,7 +8696,7 @@
       </c>
       <c r="M56" s="137"/>
     </row>
-    <row r="57" spans="1:13" s="132" customFormat="1" ht="87">
+    <row r="57" spans="1:13" s="132" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="130" t="s">
         <v>318</v>
       </c>
@@ -8727,7 +8735,7 @@
       </c>
       <c r="M57" s="146"/>
     </row>
-    <row r="58" spans="1:13" ht="87">
+    <row r="58" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>325</v>
       </c>
@@ -8762,7 +8770,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="87">
+    <row r="59" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>331</v>
       </c>
@@ -8797,7 +8805,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="87">
+    <row r="60" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>337</v>
       </c>
@@ -8832,7 +8840,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="13" customFormat="1" ht="23.25">
+    <row r="61" spans="1:13" s="13" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -8849,7 +8857,7 @@
       <c r="L61" s="180"/>
       <c r="M61" s="12"/>
     </row>
-    <row r="62" spans="1:13" ht="57.75">
+    <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>344</v>
       </c>
@@ -8884,7 +8892,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="72.75">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>350</v>
       </c>
@@ -8919,7 +8927,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="57.75">
+    <row r="64" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>356</v>
       </c>
@@ -8954,7 +8962,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="174">
+    <row r="65" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>362</v>
       </c>
@@ -8992,7 +9000,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="57.75">
+    <row r="66" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>369</v>
       </c>
@@ -9030,7 +9038,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="57.75">
+    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>376</v>
       </c>
@@ -9065,7 +9073,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="13" customFormat="1" ht="23.25">
+    <row r="68" spans="1:13" s="13" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -9082,7 +9090,7 @@
       <c r="L68" s="180"/>
       <c r="M68" s="12"/>
     </row>
-    <row r="69" spans="1:13" ht="57.75">
+    <row r="69" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>383</v>
       </c>
@@ -9117,7 +9125,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="57.75">
+    <row r="70" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>387</v>
       </c>
@@ -9152,7 +9160,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="57.75">
+    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>389</v>
       </c>
@@ -9187,7 +9195,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="29.25">
+    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="160" t="s">
         <v>393</v>
       </c>
@@ -9196,12 +9204,12 @@
       </c>
       <c r="K72" s="187"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="158"/>
       <c r="B73" s="159"/>
       <c r="K73" s="187"/>
     </row>
-    <row r="74" spans="1:13" s="13" customFormat="1" ht="23.25">
+    <row r="74" spans="1:13" s="13" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -9218,7 +9226,7 @@
       <c r="L74" s="180"/>
       <c r="M74" s="12"/>
     </row>
-    <row r="75" spans="1:13" ht="72.75">
+    <row r="75" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>396</v>
       </c>
@@ -9253,7 +9261,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="72.75">
+    <row r="76" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>401</v>
       </c>
@@ -9288,7 +9296,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="57.75">
+    <row r="77" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>403</v>
       </c>
@@ -9323,7 +9331,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="29.25">
+    <row r="78" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="160" t="s">
         <v>393</v>
       </c>
@@ -9332,12 +9340,12 @@
       </c>
       <c r="K78" s="186"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="158"/>
       <c r="B79" s="159"/>
       <c r="K79" s="186"/>
     </row>
-    <row r="80" spans="1:13" s="13" customFormat="1" ht="23.25">
+    <row r="80" spans="1:13" s="13" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -9354,7 +9362,7 @@
       <c r="L80" s="180"/>
       <c r="M80" s="12"/>
     </row>
-    <row r="81" spans="1:11" ht="72.75">
+    <row r="81" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>409</v>
       </c>
@@ -9389,7 +9397,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="57.75">
+    <row r="82" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>414</v>
       </c>
@@ -9424,7 +9432,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="57.75">
+    <row r="83" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>415</v>
       </c>
@@ -9459,7 +9467,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="144.75">
+    <row r="84" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>418</v>
       </c>
@@ -9494,7 +9502,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="144.75">
+    <row r="85" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>424</v>
       </c>
@@ -9529,7 +9537,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="144.75">
+    <row r="86" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
         <v>428</v>
       </c>
@@ -9564,7 +9572,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="87">
+    <row r="87" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="29" t="s">
         <v>433</v>
       </c>
@@ -9599,7 +9607,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="144.75">
+    <row r="88" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A88" s="29" t="s">
         <v>438</v>
       </c>
@@ -9634,7 +9642,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="144.75">
+    <row r="89" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
         <v>442</v>
       </c>
@@ -9669,7 +9677,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="144.75">
+    <row r="90" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A90" s="29" t="s">
         <v>446</v>
       </c>
@@ -9704,7 +9712,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="144.75">
+    <row r="91" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A91" s="29" t="s">
         <v>450</v>
       </c>
@@ -9739,7 +9747,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="144.75">
+    <row r="92" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A92" s="29" t="s">
         <v>454</v>
       </c>
@@ -9774,7 +9782,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="144.75">
+    <row r="93" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A93" s="29" t="s">
         <v>458</v>
       </c>
@@ -9809,7 +9817,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="144.75">
+    <row r="94" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
         <v>462</v>
       </c>
@@ -9844,7 +9852,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="144.75">
+    <row r="95" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
         <v>466</v>
       </c>
@@ -9879,7 +9887,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="144.75">
+    <row r="96" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
         <v>470</v>
       </c>
@@ -9922,23 +9930,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3314DC-EE1F-4F98-920F-5236415E2BA0}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" customWidth="1"/>
-    <col min="6" max="6" width="37.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="10" width="28.85546875" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="38.44140625" customWidth="1"/>
+    <col min="6" max="6" width="37.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="10" width="28.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" customWidth="1"/>
+    <col min="12" max="12" width="37.5546875" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.25" customHeight="1">
+    <row r="1" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="190" t="s">
         <v>476</v>
       </c>
@@ -9955,7 +9963,7 @@
       <c r="L1" s="190"/>
       <c r="M1" s="190"/>
     </row>
-    <row r="2" spans="1:13" ht="30.75" customHeight="1">
+    <row r="2" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="47" t="s">
         <v>0</v>
       </c>
@@ -9996,7 +10004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="303.75" customHeight="1">
+    <row r="3" spans="1:13" ht="303.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="41" t="s">
         <v>477</v>
       </c>
@@ -10033,7 +10041,7 @@
       <c r="L3" s="42"/>
       <c r="M3" s="50"/>
     </row>
-    <row r="4" spans="1:13" ht="302.25" customHeight="1">
+    <row r="4" spans="1:13" ht="302.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>485</v>
       </c>
@@ -10070,7 +10078,7 @@
       <c r="L4" s="42"/>
       <c r="M4" s="50"/>
     </row>
-    <row r="5" spans="1:13" ht="226.5">
+    <row r="5" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="s">
         <v>492</v>
       </c>
@@ -10107,7 +10115,7 @@
       <c r="L5" s="42"/>
       <c r="M5" s="119"/>
     </row>
-    <row r="6" spans="1:13" ht="226.5">
+    <row r="6" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>499</v>
       </c>
@@ -10144,7 +10152,7 @@
       <c r="L6" s="42"/>
       <c r="M6" s="50"/>
     </row>
-    <row r="7" spans="1:13" ht="226.5">
+    <row r="7" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
         <v>506</v>
       </c>
@@ -10181,7 +10189,7 @@
       <c r="L7" s="42"/>
       <c r="M7" s="50"/>
     </row>
-    <row r="8" spans="1:13" ht="308.25" customHeight="1">
+    <row r="8" spans="1:13" ht="308.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>513</v>
       </c>
@@ -10218,7 +10226,7 @@
       <c r="L8" s="42"/>
       <c r="M8" s="50"/>
     </row>
-    <row r="9" spans="1:13" ht="319.5" customHeight="1">
+    <row r="9" spans="1:13" ht="319.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="s">
         <v>520</v>
       </c>
@@ -10255,7 +10263,7 @@
       <c r="L9" s="42"/>
       <c r="M9" s="50"/>
     </row>
-    <row r="10" spans="1:13" ht="303" customHeight="1">
+    <row r="10" spans="1:13" ht="303" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>527</v>
       </c>
@@ -10289,10 +10297,12 @@
       <c r="K10" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="L10" s="42"/>
+      <c r="L10" s="42" t="s">
+        <v>868</v>
+      </c>
       <c r="M10" s="50"/>
     </row>
-    <row r="11" spans="1:13" ht="303" customHeight="1">
+    <row r="11" spans="1:13" ht="303" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41" t="s">
         <v>534</v>
       </c>
@@ -10329,7 +10339,7 @@
       <c r="L11" s="42"/>
       <c r="M11" s="50"/>
     </row>
-    <row r="12" spans="1:13" ht="291.75" customHeight="1">
+    <row r="12" spans="1:13" ht="291.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>541</v>
       </c>
@@ -10366,7 +10376,7 @@
       <c r="L12" s="42"/>
       <c r="M12" s="50"/>
     </row>
-    <row r="13" spans="1:13" ht="309" customHeight="1">
+    <row r="13" spans="1:13" ht="309" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41" t="s">
         <v>548</v>
       </c>
@@ -10403,7 +10413,7 @@
       <c r="L13" s="42"/>
       <c r="M13" s="50"/>
     </row>
-    <row r="14" spans="1:13" ht="320.25" customHeight="1">
+    <row r="14" spans="1:13" ht="320.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>555</v>
       </c>
@@ -10440,7 +10450,7 @@
       <c r="L14" s="42"/>
       <c r="M14" s="50"/>
     </row>
-    <row r="15" spans="1:13" ht="328.5" customHeight="1">
+    <row r="15" spans="1:13" ht="328.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="41" t="s">
         <v>562</v>
       </c>
@@ -10477,7 +10487,7 @@
       <c r="L15" s="42"/>
       <c r="M15" s="50"/>
     </row>
-    <row r="16" spans="1:13" ht="226.5">
+    <row r="16" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>569</v>
       </c>
@@ -10512,7 +10522,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="226.5">
+    <row r="17" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="41" t="s">
         <v>576</v>
       </c>
@@ -10548,7 +10558,7 @@
       </c>
       <c r="M17" s="49"/>
     </row>
-    <row r="18" spans="1:14" ht="226.5">
+    <row r="18" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>583</v>
       </c>
@@ -10584,7 +10594,7 @@
       </c>
       <c r="M18" s="49"/>
     </row>
-    <row r="19" spans="1:14" ht="246">
+    <row r="19" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A19" s="41" t="s">
         <v>590</v>
       </c>
@@ -10620,7 +10630,7 @@
       </c>
       <c r="M19" s="49"/>
     </row>
-    <row r="20" spans="1:14" ht="226.5">
+    <row r="20" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>597</v>
       </c>
@@ -10656,7 +10666,7 @@
       </c>
       <c r="M20" s="49"/>
     </row>
-    <row r="21" spans="1:14" ht="226.5">
+    <row r="21" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>604</v>
       </c>
@@ -10692,7 +10702,7 @@
       </c>
       <c r="M21" s="49"/>
     </row>
-    <row r="22" spans="1:14" ht="33.75">
+    <row r="22" spans="1:14" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A22" s="190" t="s">
         <v>611</v>
       </c>
@@ -10709,7 +10719,7 @@
       <c r="L22" s="190"/>
       <c r="M22" s="190"/>
     </row>
-    <row r="23" spans="1:14" ht="31.5" customHeight="1">
+    <row r="23" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>0</v>
       </c>
@@ -10750,7 +10760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="94.5">
+    <row r="24" spans="1:14" ht="90" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>612</v>
       </c>
@@ -10785,7 +10795,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="133.5" customHeight="1">
+    <row r="25" spans="1:14" ht="133.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="s">
         <v>620</v>
       </c>
@@ -10821,7 +10831,7 @@
       </c>
       <c r="M25" s="49"/>
     </row>
-    <row r="26" spans="1:14" ht="141" customHeight="1">
+    <row r="26" spans="1:14" ht="141" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>626</v>
       </c>
@@ -10857,7 +10867,7 @@
       </c>
       <c r="M26" s="157"/>
     </row>
-    <row r="27" spans="1:14" ht="33.75">
+    <row r="27" spans="1:14" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A27" s="190" t="s">
         <v>631</v>
       </c>
@@ -10874,7 +10884,7 @@
       <c r="L27" s="190"/>
       <c r="M27" s="190"/>
     </row>
-    <row r="28" spans="1:14" ht="21">
+    <row r="28" spans="1:14" ht="21" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>0</v>
       </c>
@@ -10915,7 +10925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="257.25" customHeight="1">
+    <row r="29" spans="1:14" ht="257.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>632</v>
       </c>
@@ -10950,7 +10960,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="151.5">
+    <row r="30" spans="1:14" ht="126" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>640</v>
       </c>
@@ -10986,7 +10996,7 @@
       </c>
       <c r="N30" s="11"/>
     </row>
-    <row r="31" spans="1:14" ht="33.75">
+    <row r="31" spans="1:14" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A31" s="190" t="s">
         <v>645</v>
       </c>
@@ -11003,7 +11013,7 @@
       <c r="L31" s="190"/>
       <c r="M31" s="190"/>
     </row>
-    <row r="32" spans="1:14" ht="21">
+    <row r="32" spans="1:14" ht="21" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>0</v>
       </c>
@@ -11044,7 +11054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="113.25">
+    <row r="33" spans="1:11" ht="108" x14ac:dyDescent="0.3">
       <c r="A33" s="41" t="s">
         <v>646</v>
       </c>
@@ -11098,24 +11108,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD8D6CB-C9E6-4626-86C0-8C18E6997854}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="22.109375" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11156,7 +11166,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="72.75">
+    <row r="2" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>653</v>
       </c>
@@ -11194,7 +11204,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="57.75">
+    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>663</v>
       </c>
@@ -11232,7 +11242,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="72.75">
+    <row r="4" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>671</v>
       </c>
@@ -11270,7 +11280,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.5">
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>680</v>
       </c>
@@ -11308,7 +11318,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="57.75">
+    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>686</v>
       </c>
@@ -11344,7 +11354,7 @@
       </c>
       <c r="M6" s="9"/>
     </row>
-    <row r="7" spans="1:13" ht="57.75">
+    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>693</v>
       </c>
@@ -11382,7 +11392,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="43.5">
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>701</v>
       </c>
@@ -11418,7 +11428,7 @@
       </c>
       <c r="M8" s="9"/>
     </row>
-    <row r="9" spans="1:13" ht="43.5">
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>708</v>
       </c>
@@ -11454,7 +11464,7 @@
       </c>
       <c r="M9" s="9"/>
     </row>
-    <row r="10" spans="1:13" ht="57.75">
+    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>715</v>
       </c>
@@ -11492,7 +11502,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="43.5">
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>723</v>
       </c>
@@ -11528,7 +11538,7 @@
       </c>
       <c r="M11" s="9"/>
     </row>
-    <row r="12" spans="1:13" ht="23.25">
+    <row r="12" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A12" s="115"/>
       <c r="B12" s="116"/>
       <c r="C12" s="116"/>
@@ -11545,7 +11555,7 @@
       <c r="L12" s="116"/>
       <c r="M12" s="116"/>
     </row>
-    <row r="13" spans="1:13" s="9" customFormat="1" ht="57.75">
+    <row r="13" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>730</v>
       </c>
@@ -11580,7 +11590,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="14" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>736</v>
       </c>
@@ -11615,7 +11625,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="15" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>743</v>
       </c>
@@ -11650,7 +11660,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="9" customFormat="1" ht="57.75">
+    <row r="16" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>748</v>
       </c>
@@ -11688,7 +11698,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="17" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>756</v>
       </c>
@@ -11726,7 +11736,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="18" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>763</v>
       </c>
@@ -11764,7 +11774,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="19" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>770</v>
       </c>
@@ -11802,7 +11812,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="20" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>776</v>
       </c>
@@ -11837,7 +11847,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="9" customFormat="1" ht="43.5">
+    <row r="21" spans="1:13" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>782</v>
       </c>
@@ -11875,7 +11885,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="9" customFormat="1" ht="57.75">
+    <row r="22" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>788</v>
       </c>
@@ -11913,7 +11923,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="9" customFormat="1" ht="115.5">
+    <row r="23" spans="1:13" s="9" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>795</v>
       </c>
@@ -11961,24 +11971,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2302F9-8F3A-44F1-9393-C625F36C117E}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="22.109375" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12019,7 +12029,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75">
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="K2" s="3" t="s">
         <v>183</v>
       </c>
@@ -12037,24 +12047,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B224FC6-5C06-40B3-B0A7-694006569755}">
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
-    <col min="3" max="3" width="52.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" customWidth="1"/>
+    <col min="3" max="3" width="52.88671875" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
     <col min="5" max="5" width="82" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="64.5703125" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="64.5546875" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12095,7 +12105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="39" customHeight="1">
+    <row r="2" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>802</v>
       </c>
@@ -12125,7 +12135,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>808</v>
       </c>
@@ -12154,7 +12164,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>813</v>
       </c>
@@ -12183,7 +12193,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>818</v>
       </c>
@@ -12212,7 +12222,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>824</v>
       </c>
@@ -12241,7 +12251,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>829</v>
       </c>
@@ -12270,7 +12280,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>834</v>
       </c>
@@ -12299,7 +12309,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>839</v>
       </c>
@@ -12328,7 +12338,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>844</v>
       </c>
@@ -12357,7 +12367,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>849</v>
       </c>
@@ -12380,7 +12390,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>853</v>
       </c>
@@ -12388,7 +12398,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>854</v>
       </c>
@@ -12396,7 +12406,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>855</v>
       </c>
@@ -12404,62 +12414,62 @@
         <v>804</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>867</v>
       </c>
